--- a/output/pdf_financials_xlsx/LBI.xlsx
+++ b/output/pdf_financials_xlsx/LBI.xlsx
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.020033</v>
+        <v>-0.020033</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.100383</v>
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.020033</v>
+        <v>-0.020033</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.100383</v>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.020033</v>
+        <v>-0.020033</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.100383</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.020033</v>
+        <v>-0.020033</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.100383</v>
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.020033</v>
+        <v>-0.020033</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.100383</v>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -5637,31 +5637,31 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-0.002342</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>-0.003538</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>-0.01504</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>-0.00263</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>0.009601</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>-0.016911</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>-0.010706</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>-0.022972</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>0.009279000000000001</v>
       </c>
     </row>
     <row r="92">
@@ -5695,28 +5695,28 @@
         <v>0.03729</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.246585</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.472557</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.511054</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.133451</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.483078</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.483078</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.483078</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.483078</v>
       </c>
     </row>
     <row r="93">
@@ -6008,7 +6008,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>0.020033</v>
+        <v>-0.020033</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.100383</v>
@@ -9910,7 +9910,11 @@
           <t>Share based payment reserves 13</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -10004,7 +10008,11 @@
           <t>Warrant reserves 13</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -10098,7 +10106,11 @@
           <t>Foreign currency translation reserves</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -11490,7 +11502,11 @@
           <t>Share based payment reserves 12</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -11584,7 +11600,11 @@
           <t>Warrant reserves 12</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -12348,7 +12368,11 @@
           <t>Share based payment reserves 11</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -12442,7 +12466,11 @@
           <t>Warrant reserves 11</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -13200,7 +13228,11 @@
           <t>Share based payment reserves 9</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -13294,7 +13326,11 @@
           <t>Warrant reserves 9</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -14346,7 +14382,11 @@
           <t>Share based payment reserve 10</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -14440,7 +14480,11 @@
           <t>Warrant reserve 10</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -14536,7 +14580,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -16498,7 +16546,11 @@
           <t>Share based payment reserve</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -54122,7 +54174,7 @@
         </is>
       </c>
       <c r="E487" s="5" t="n">
-        <v>0.020033</v>
+        <v>-0.020033</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/LBI.xlsx
+++ b/output/pdf_financials_xlsx/LBI.xlsx
@@ -892,37 +892,37 @@
         <v>0.009531</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.01165</v>
+        <v>0.100383</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.037112</v>
+        <v>0.124136</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.028287</v>
+        <v>0.075492</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.031936</v>
+        <v>0.104995</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.058243</v>
+        <v>0.111782</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.000974</v>
+        <v>0.041962</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.205854</v>
+        <v>0.244283</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.865912</v>
+        <v>1.556931</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>3.533798</v>
+        <v>1.377289</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>0.500362</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>0.87752</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>0</v>
@@ -947,37 +947,37 @@
         <v>-0.009531</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.01165</v>
+        <v>-0.100383</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.037112</v>
+        <v>-0.124136</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.028287</v>
+        <v>-0.075492</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.031936</v>
+        <v>-0.104995</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.058243</v>
+        <v>-0.111782</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.000974</v>
+        <v>-0.041962</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.205854</v>
+        <v>-0.244283</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.865912</v>
+        <v>-1.556931</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-3.533798</v>
+        <v>-1.377289</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0</v>
+        <v>-0.500362</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0</v>
+        <v>-0.87752</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>0</v>
@@ -2337,52 +2337,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.099998</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.17127</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.035827</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.055492</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.027414</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.005686</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.006759</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.138436</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.057568</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.014286</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.00667</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.182329</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.5537300000000001</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.06704499999999999</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.021445</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.005393</v>
       </c>
     </row>
     <row r="35">
@@ -2447,52 +2447,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.099998</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.17127</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.035827</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.055492</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.027414</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.005686</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.006759</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.138436</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.057568</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.014286</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.00667</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.182329</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.5537300000000001</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.06704499999999999</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.021445</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.005393</v>
       </c>
     </row>
     <row r="37">
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.099998</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.17127</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -3128,31 +3128,31 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.146716</v>
+        <v>2.00828</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>5.242547</v>
+        <v>5.184979</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.568216</v>
+        <v>2.55393</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.490805</v>
+        <v>3.484135</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>13.183751</v>
+        <v>12.630021</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>7.416301</v>
+        <v>7.349256</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.315545</v>
+        <v>2.2941</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.908107</v>
+        <v>1.902714</v>
       </c>
     </row>
     <row r="49">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15046,7 +15046,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
@@ -45826,7 +45826,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -45875,13 +45875,13 @@
         </is>
       </c>
       <c r="N399" s="5" t="n">
-        <v>-1.377289</v>
+        <v>1.377289</v>
       </c>
       <c r="O399" s="5" t="n">
-        <v>-0.500362</v>
+        <v>0.500362</v>
       </c>
       <c r="P399" s="5" t="n">
-        <v>-0.87752</v>
+        <v>0.87752</v>
       </c>
       <c r="Q399" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -50840,7 +50840,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -53402,7 +53402,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">

--- a/output/pdf_financials_xlsx/LBI.xlsx
+++ b/output/pdf_financials_xlsx/LBI.xlsx
@@ -17674,7 +17674,11 @@
           <t>Share capital – Note 8</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LBI.xlsx
+++ b/output/pdf_financials_xlsx/LBI.xlsx
@@ -745,31 +745,31 @@
         <v>0.000974</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.050446</v>
+        <v>0.004978</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0</v>
+        <v>0.085109</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>0.306162</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0</v>
+        <v>0.174985</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0</v>
+        <v>0.181347</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0</v>
+        <v>0.264581</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0</v>
+        <v>0.264462</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0</v>
+        <v>0.266209</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0</v>
+        <v>0.272101</v>
       </c>
     </row>
     <row r="8">
@@ -925,16 +925,16 @@
         <v>0.87752</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>0.264581</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>0.264462</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>0.266209</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>0.272101</v>
       </c>
     </row>
     <row r="11">
@@ -980,16 +980,16 @@
         <v>-0.87752</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0</v>
+        <v>-0.264581</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0</v>
+        <v>-0.264462</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0</v>
+        <v>-0.266209</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0</v>
+        <v>-0.272101</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
         <v>-3.255326</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-3.181733</v>
+        <v>-2.989952</v>
       </c>
     </row>
     <row r="17">
@@ -1310,7 +1310,7 @@
         <v>1.247415</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0.120811</v>
+        <v>0.09429899999999999</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>-0.942522</v>
@@ -1319,7 +1319,7 @@
         <v>0.126336</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.191781</v>
       </c>
     </row>
     <row r="18">
@@ -1981,7 +1981,7 @@
         <v>-3.255326</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-3.181733</v>
+        <v>-2.989952</v>
       </c>
     </row>
     <row r="28">
@@ -2091,7 +2091,7 @@
         <v>-3.255326</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-3.181733</v>
+        <v>-2.989952</v>
       </c>
     </row>
     <row r="30">
@@ -2224,7 +2224,7 @@
         <v>16.89934255384552</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-3415.634718688154</v>
+        <v>-2666.07294317218</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>-15.98211130547316</v>
@@ -2233,7 +2233,7 @@
         <v>-3.880901636272374</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0</v>
+        <v>-6.414183237724218</v>
       </c>
     </row>
     <row r="32">
@@ -6475,7 +6475,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>0.225972</v>
       </c>
       <c r="L107" s="3" t="n">
         <v>0</v>
@@ -6484,7 +6484,7 @@
         <v>0</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>0.097147</v>
       </c>
       <c r="O107" s="3" t="n">
         <v>0</v>
@@ -6646,16 +6646,16 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.019293</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.249756</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.123459</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.075143</v>
       </c>
       <c r="Q110" s="3" t="n">
         <v>0</v>
@@ -6909,13 +6909,13 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.805985</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>2.338104</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
@@ -21798,7 +21798,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -25102,7 +25106,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -26346,7 +26354,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -27690,7 +27702,11 @@
           <t>Share-based payment expense</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -30344,7 +30360,11 @@
           <t>Proceeds from disposal of marketable securities</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -33002,7 +33022,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -33858,7 +33882,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -35192,7 +35220,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -36152,7 +36184,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -36636,7 +36672,11 @@
           <t>Gross proceeds from private placement</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -37512,7 +37552,11 @@
           <t>Gross proceeds from private placement 200,000</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E311" s="5" t="n">
         <v>0.1</v>
       </c>
@@ -40104,7 +40148,11 @@
           <t>Directors fees (note 16)</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -40176,10 +40224,10 @@
         </is>
       </c>
       <c r="S338" s="5" t="n">
-        <v>-0.266209</v>
+        <v>0.266209</v>
       </c>
       <c r="T338" s="5" t="n">
-        <v>-0.272101</v>
+        <v>0.272101</v>
       </c>
     </row>
     <row r="339">
@@ -40374,7 +40422,11 @@
           <t>INCOME TAX RECOVERY (EXPENSE) (note 17)</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -42316,7 +42368,11 @@
           <t>Director’s fees (note 15)</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -42383,10 +42439,10 @@
         </is>
       </c>
       <c r="R362" s="5" t="n">
-        <v>-0.264462</v>
+        <v>0.264462</v>
       </c>
       <c r="S362" s="5" t="n">
-        <v>-0.266209</v>
+        <v>0.266209</v>
       </c>
       <c r="T362" t="inlineStr">
         <is>
@@ -43832,7 +43888,11 @@
           <t>Director’s fees (note 14)</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -43894,10 +43954,10 @@
         </is>
       </c>
       <c r="Q378" s="5" t="n">
-        <v>-0.264581</v>
+        <v>0.264581</v>
       </c>
       <c r="R378" s="5" t="n">
-        <v>-0.264462</v>
+        <v>0.264462</v>
       </c>
       <c r="S378" t="inlineStr">
         <is>
@@ -44214,7 +44274,11 @@
           <t>INCOME TAX RECOVERY (EXPENSE) (note 15)</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
@@ -45162,7 +45226,11 @@
           <t>Director’s fees</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -45209,13 +45277,13 @@
         </is>
       </c>
       <c r="N392" s="5" t="n">
-        <v>-0.306162</v>
+        <v>0.306162</v>
       </c>
       <c r="O392" s="5" t="n">
-        <v>-0.174985</v>
+        <v>0.174985</v>
       </c>
       <c r="P392" s="5" t="n">
-        <v>-0.181347</v>
+        <v>0.181347</v>
       </c>
       <c r="Q392" t="inlineStr">
         <is>
@@ -48606,7 +48674,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
